--- a/artfynd/A 47313-2023 artfynd.xlsx
+++ b/artfynd/A 47313-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7180388</v>
+        <v>7180395</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näverliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516711.5334585364</v>
+        <v>516901</v>
       </c>
       <c r="R2" t="n">
-        <v>7262827.824102088</v>
+        <v>7262553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,19 +746,9 @@
           <t>2010-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +757,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,21 +765,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -811,6 +777,111 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7180396</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Näverliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>516901</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7262553</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2010-08-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2010-08-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
